--- a/data/trans_camb/P12_3_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P12_3_R-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,54; 10,31</t>
+          <t>1,0; 10,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,39; 11,16</t>
+          <t>1,53; 11,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,06; -3,3</t>
+          <t>-9,19; -3,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13,57; 26,65</t>
+          <t>13,85; 26,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,78; 17,08</t>
+          <t>6,08; 16,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,69; -3,01</t>
+          <t>-9,73; -3,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,58; 16,31</t>
+          <t>8,74; 16,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,81; 12,61</t>
+          <t>5,28; 12,73</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-8,37; -3,92</t>
+          <t>-8,01; -3,82</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,29; 286,4</t>
+          <t>6,25; 298,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,3; 294,02</t>
+          <t>16,18; 298,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -798,32 +798,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>148,83; 549,47</t>
+          <t>124,36; 548,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>62,36; 369,08</t>
+          <t>65,56; 373,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-95,69; -65,23</t>
+          <t>-95,27; -62,9</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>105,38; 344,16</t>
+          <t>106,82; 339,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>59,95; 261,01</t>
+          <t>63,4; 274,48</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-97,37; -83,26</t>
+          <t>-97,33; -81,69</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 2,44</t>
+          <t>-4,44; 2,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,18; -1,11</t>
+          <t>-7,12; -1,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 1,84</t>
+          <t>-5,76; 1,79</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 1,41</t>
+          <t>-6,89; 1,22</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,45; -2,35</t>
+          <t>-10,23; -2,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,31; -1,82</t>
+          <t>-9,32; -1,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 0,81</t>
+          <t>-4,64; 0,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,65; -2,69</t>
+          <t>-7,63; -2,71</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-6,45; -1,09</t>
+          <t>-6,37; -1,13</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-44,58; 43,12</t>
+          <t>-44,66; 41,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-71,19; -15,76</t>
+          <t>-69,91; -14,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-58,06; 30,66</t>
+          <t>-59,79; 32,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-42,07; 13,15</t>
+          <t>-43,5; 9,79</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-64,31; -17,88</t>
+          <t>-63,8; -21,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-56,04; -13,72</t>
+          <t>-56,99; -13,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-36,8; 9,19</t>
+          <t>-37,77; 10,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-61,08; -26,89</t>
+          <t>-60,9; -26,91</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-52,05; -10,65</t>
+          <t>-52,0; -12,16</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,18; 7,95</t>
+          <t>2,38; 8,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,53; 6,66</t>
+          <t>1,71; 6,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,54; 8,96</t>
+          <t>3,7; 9,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,16; 13,75</t>
+          <t>5,98; 13,53</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,33; 5,79</t>
+          <t>0,51; 5,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,47; 13,33</t>
+          <t>7,26; 13,43</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,99; 9,98</t>
+          <t>5,05; 9,78</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,74; 5,56</t>
+          <t>1,68; 5,25</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,29; 10,4</t>
+          <t>6,33; 10,36</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>48,12; —</t>
+          <t>7,55; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-9,75; —</t>
+          <t>-13,34; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>87,79; —</t>
+          <t>97,81; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>177,14; 1565,39</t>
+          <t>172,44; 1896,29</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-6,4; 707,6</t>
+          <t>9,65; 754,04</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>199,96; 1732,75</t>
+          <t>212,82; 1876,25</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>203,2; 1486,29</t>
+          <t>222,61; 1537,95</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>65,9; 764,34</t>
+          <t>56,53; 756,14</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>249,46; 1651,22</t>
+          <t>254,23; 1586,22</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,32; 12,32</t>
+          <t>5,36; 12,11</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,19; 8,71</t>
+          <t>3,09; 8,69</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,42; 7,45</t>
+          <t>1,38; 7,75</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12,45; 22,13</t>
+          <t>13,11; 22,05</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,92; 18,06</t>
+          <t>9,24; 17,89</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,09; 9,77</t>
+          <t>1,43; 9,98</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,14; 15,95</t>
+          <t>9,78; 15,96</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,26; 12,67</t>
+          <t>6,94; 12,43</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,63; 8,03</t>
+          <t>2,61; 7,71</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>202,0; 2957,0</t>
+          <t>182,92; 2977,48</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>102,77; 2260,3</t>
+          <t>102,54; 1670,6</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,58; 1558,98</t>
+          <t>24,74; 1304,67</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>192,13; 840,93</t>
+          <t>213,09; 830,51</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>136,93; 695,38</t>
+          <t>152,21; 674,95</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,04; 368,91</t>
+          <t>23,95; 362,11</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>274,56; 836,52</t>
+          <t>246,51; 837,59</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>180,8; 667,66</t>
+          <t>181,39; 658,47</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>68,15; 414,48</t>
+          <t>70,41; 393,79</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-11,87; -1,44</t>
+          <t>-11,93; -1,62</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 9,89</t>
+          <t>-3,22; 9,45</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 11,27</t>
+          <t>-1,87; 10,71</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-10,96; 3,03</t>
+          <t>-10,96; 2,56</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 14,21</t>
+          <t>-1,6; 14,02</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-9,13; 4,01</t>
+          <t>-8,37; 3,97</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-9,58; -0,33</t>
+          <t>-9,41; -0,87</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 9,82</t>
+          <t>-0,54; 9,95</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 5,62</t>
+          <t>-3,42; 5,65</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-81,39; -12,93</t>
+          <t>-81,09; -16,93</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-21,0; 120,95</t>
+          <t>-22,15; 105,73</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-11,57; 141,52</t>
+          <t>-14,34; 128,62</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-51,86; 24,23</t>
+          <t>-52,89; 18,72</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 108,99</t>
+          <t>-7,73; 104,69</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-39,69; 29,65</t>
+          <t>-38,02; 30,83</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-58,02; -3,49</t>
+          <t>-57,9; -8,39</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 79,88</t>
+          <t>-4,03; 83,86</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-19,88; 47,63</t>
+          <t>-20,26; 47,09</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>4,61; 11,56</t>
+          <t>4,9; 11,68</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>3,61; 9,83</t>
+          <t>3,47; 9,57</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4,66; 10,39</t>
+          <t>4,78; 10,36</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3,32; 11,85</t>
+          <t>2,98; 11,56</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>5,25; 15,22</t>
+          <t>5,39; 15,57</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,17; 13,71</t>
+          <t>6,17; 13,44</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,35; 10,64</t>
+          <t>5,1; 10,52</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>5,43; 11,28</t>
+          <t>5,37; 11,14</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>6,38; 10,8</t>
+          <t>6,26; 10,89</t>
         </is>
       </c>
     </row>
@@ -1878,32 +1878,32 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>52,86; 669,8</t>
+          <t>48,06; 661,35</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>106,77; 799,04</t>
+          <t>88,99; 726,36</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>103,41; 786,11</t>
+          <t>101,65; 784,4</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>163,62; 932,34</t>
+          <t>176,61; 991,51</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>190,15; 990,32</t>
+          <t>177,9; 993,12</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>202,07; 991,69</t>
+          <t>207,6; 1022,05</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 3,84</t>
+          <t>-1,26; 3,94</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,83; 6,39</t>
+          <t>0,63; 6,34</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>8,34; 16,97</t>
+          <t>8,24; 16,96</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,02; 5,67</t>
+          <t>0,23; 5,56</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2,35; 8,59</t>
+          <t>2,83; 9,09</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,26; 13,89</t>
+          <t>1,16; 14,0</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,23; 4,09</t>
+          <t>0,28; 4,15</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>2,45; 6,69</t>
+          <t>2,71; 6,61</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>4,03; 13,34</t>
+          <t>4,22; 13,25</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-21,93; 127,49</t>
+          <t>-21,85; 134,08</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>10,3; 192,38</t>
+          <t>7,33; 206,71</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>142,6; 513,58</t>
+          <t>132,55; 541,68</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 139,52</t>
+          <t>2,17; 143,19</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>35,28; 210,74</t>
+          <t>41,8; 224,32</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>19,33; 302,83</t>
+          <t>25,42; 307,49</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,38; 97,85</t>
+          <t>4,02; 105,24</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>41,06; 162,71</t>
+          <t>49,38; 173,24</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>88,09; 313,68</t>
+          <t>87,28; 314,82</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>0,6; 6,31</t>
+          <t>0,64; 6,61</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 2,1</t>
+          <t>-2,74; 2,46</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 11,53</t>
+          <t>-1,85; 11,95</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 3,12</t>
+          <t>-3,7; 3,31</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-6,27; -0,04</t>
+          <t>-6,31; -0,14</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>6,05; 13,24</t>
+          <t>6,38; 13,57</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 3,79</t>
+          <t>-0,62; 3,95</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 0,51</t>
+          <t>-3,91; 0,15</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,84; 10,94</t>
+          <t>0,55; 10,95</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>7,21; 109,03</t>
+          <t>7,1; 123,37</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-35,84; 34,93</t>
+          <t>-32,09; 44,42</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-26,09; 177,62</t>
+          <t>-18,69; 189,4</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-23,64; 28,47</t>
+          <t>-26,63; 30,48</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-44,15; -0,07</t>
+          <t>-45,58; -0,95</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>41,28; 125,23</t>
+          <t>44,1; 126,61</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-7,8; 42,26</t>
+          <t>-5,73; 43,08</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-34,69; 6,69</t>
+          <t>-34,33; 2,0</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>8,94; 116,21</t>
+          <t>12,99; 116,45</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>1,77; 4,26</t>
+          <t>1,86; 4,32</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>1,09; 3,55</t>
+          <t>1,15; 3,59</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2,42; 6,39</t>
+          <t>2,45; 6,3</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3,37; 6,41</t>
+          <t>3,32; 6,28</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>1,74; 4,58</t>
+          <t>1,8; 4,79</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,25; 6,31</t>
+          <t>2,07; 6,22</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>3,01; 4,97</t>
+          <t>2,96; 4,94</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>1,89; 3,79</t>
+          <t>1,87; 3,79</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>3,25; 5,91</t>
+          <t>3,07; 5,88</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>31,11; 95,5</t>
+          <t>32,08; 92,47</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>18,88; 76,73</t>
+          <t>20,74; 77,12</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>47,95; 140,92</t>
+          <t>47,55; 137,08</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>36,74; 81,02</t>
+          <t>36,02; 80,83</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>18,78; 59,04</t>
+          <t>19,76; 61,45</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>26,59; 81,16</t>
+          <t>24,13; 80,3</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>41,3; 80,8</t>
+          <t>40,17; 78,25</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>26,8; 59,55</t>
+          <t>26,48; 61,25</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>45,97; 91,81</t>
+          <t>44,83; 91,64</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P12_3_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P12_3_R-Provincia-trans_camb.xlsx
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-5,86</t>
+          <t>-5,73</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-5,75</t>
+          <t>-5,68</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 10,73</t>
+          <t>1,06; 10,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,53; 11,53</t>
+          <t>1,82; 11,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,19; -3,18</t>
+          <t>-8,77; -3,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13,85; 26,51</t>
+          <t>13,26; 25,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,08; 16,94</t>
+          <t>5,05; 16,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,73; -3,13</t>
+          <t>-9,42; -2,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,74; 16,39</t>
+          <t>8,56; 16,73</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,28; 12,73</t>
+          <t>5,26; 12,39</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-8,01; -3,82</t>
+          <t>-8,1; -3,7</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-86,02%</t>
+          <t>-84,18%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-92,61%</t>
+          <t>-91,37%</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,25; 298,11</t>
+          <t>4,62; 268,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,18; 298,77</t>
+          <t>16,7; 298,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -798,32 +798,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>124,36; 548,06</t>
+          <t>129,59; 541,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>65,56; 373,94</t>
+          <t>44,7; 335,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-95,27; -62,9</t>
+          <t>-94,33; -59,15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>106,82; 339,74</t>
+          <t>103,5; 347,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>63,4; 274,48</t>
+          <t>65,07; 257,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-97,33; -81,69</t>
+          <t>-96,58; -80,01</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-2,26</t>
+          <t>-2,4</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-5,35</t>
+          <t>-5,61</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-3,84</t>
+          <t>-4,02</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 2,61</t>
+          <t>-4,18; 2,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,12; -1,03</t>
+          <t>-6,79; -0,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 1,79</t>
+          <t>-5,77; 1,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,89; 1,22</t>
+          <t>-7,19; 1,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,23; -2,47</t>
+          <t>-10,26; -2,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,32; -1,71</t>
+          <t>-9,72; -2,46</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 0,99</t>
+          <t>-4,64; 1,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,63; -2,71</t>
+          <t>-7,59; -2,74</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-6,37; -1,13</t>
+          <t>-6,64; -1,5</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-28,06%</t>
+          <t>-29,87%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-38,49%</t>
+          <t>-40,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-34,91%</t>
+          <t>-36,53%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-44,66; 41,66</t>
+          <t>-42,55; 41,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-69,91; -14,35</t>
+          <t>-69,47; -10,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-59,79; 32,35</t>
+          <t>-58,76; 20,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-43,5; 9,79</t>
+          <t>-44,08; 13,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-63,8; -21,04</t>
+          <t>-63,41; -20,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-56,99; -13,18</t>
+          <t>-58,89; -19,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-37,77; 10,21</t>
+          <t>-36,83; 11,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-60,9; -26,91</t>
+          <t>-60,67; -28,47</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-52,0; -12,16</t>
+          <t>-53,06; -15,96</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6,23</t>
+          <t>6,61</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,22</t>
+          <t>10,49</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8,33</t>
+          <t>8,68</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,38; 8,11</t>
+          <t>2,29; 8,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,71; 6,76</t>
+          <t>1,75; 7,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,7; 9,26</t>
+          <t>3,76; 9,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,98; 13,53</t>
+          <t>6,18; 13,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,51; 5,88</t>
+          <t>0,69; 5,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,26; 13,43</t>
+          <t>7,36; 13,45</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,05; 9,78</t>
+          <t>4,97; 9,97</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,68; 5,25</t>
+          <t>1,73; 5,59</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,33; 10,36</t>
+          <t>6,63; 10,73</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>747,07%</t>
+          <t>792,77%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>598,39%</t>
+          <t>613,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>649,85%</t>
+          <t>676,76%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,55; —</t>
+          <t>48,8; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-13,34; —</t>
+          <t>13,79; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>97,81; —</t>
+          <t>102,06; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>172,44; 1896,29</t>
+          <t>154,33; 1536,05</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,65; 754,04</t>
+          <t>-15,29; 664,71</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>212,82; 1876,25</t>
+          <t>201,55; 2002,02</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>222,61; 1537,95</t>
+          <t>224,24; 1450,71</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>56,53; 756,14</t>
+          <t>68,98; 847,04</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>254,23; 1586,22</t>
+          <t>278,43; 1595,31</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4,15</t>
+          <t>4,51</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,59</t>
+          <t>8,01</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5,28</t>
+          <t>6,44</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,36; 12,11</t>
+          <t>5,39; 12,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,09; 8,69</t>
+          <t>3,29; 8,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,38; 7,75</t>
+          <t>1,81; 8,51</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13,11; 22,05</t>
+          <t>12,92; 21,77</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,24; 17,89</t>
+          <t>9,3; 17,99</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,43; 9,98</t>
+          <t>4,66; 11,81</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,78; 15,96</t>
+          <t>10,19; 16,11</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,94; 12,43</t>
+          <t>7,03; 12,62</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,61; 7,71</t>
+          <t>4,2; 9,44</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>330,78%</t>
+          <t>360,18%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>140,13%</t>
+          <t>200,83%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>199,73%</t>
+          <t>243,45%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>182,92; 2977,48</t>
+          <t>166,84; 3134,85</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>102,54; 1670,6</t>
+          <t>86,41; 1943,0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>24,74; 1304,67</t>
+          <t>11,98; 1533,79</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>213,09; 830,51</t>
+          <t>216,2; 857,24</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>152,21; 674,95</t>
+          <t>157,1; 714,87</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,95; 362,11</t>
+          <t>75,32; 458,37</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>246,51; 837,59</t>
+          <t>267,57; 841,07</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>181,39; 658,47</t>
+          <t>201,87; 700,85</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>70,41; 393,79</t>
+          <t>105,18; 490,27</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4,69</t>
+          <t>4,84</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-2,13</t>
+          <t>-2,14</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1,22</t>
+          <t>1,3</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-11,93; -1,62</t>
+          <t>-11,65; -1,67</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 9,45</t>
+          <t>-3,29; 9,48</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 10,71</t>
+          <t>-1,18; 10,57</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-10,96; 2,56</t>
+          <t>-11,44; 2,26</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 14,02</t>
+          <t>-1,83; 14,21</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-8,37; 3,97</t>
+          <t>-8,81; 4,19</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-9,41; -0,87</t>
+          <t>-9,75; -0,86</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 9,95</t>
+          <t>-0,44; 9,8</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 5,65</t>
+          <t>-3,43; 5,53</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-12,12%</t>
+          <t>-12,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,94%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-81,09; -16,93</t>
+          <t>-80,89; -18,74</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-22,15; 105,73</t>
+          <t>-23,24; 113,82</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-14,34; 128,62</t>
+          <t>-8,57; 133,68</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-52,89; 18,72</t>
+          <t>-53,48; 17,01</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 104,69</t>
+          <t>-9,21; 110,24</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-38,02; 30,83</t>
+          <t>-40,54; 30,61</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-57,9; -8,39</t>
+          <t>-57,9; -4,29</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 83,86</t>
+          <t>-3,91; 81,82</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-20,26; 47,09</t>
+          <t>-20,19; 46,63</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7,14</t>
+          <t>7,21</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,95</t>
+          <t>9,99</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>8,46</t>
+          <t>8,54</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>4,9; 11,68</t>
+          <t>5,14; 11,96</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>3,47; 9,57</t>
+          <t>3,35; 9,58</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4,78; 10,36</t>
+          <t>4,82; 10,2</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2,98; 11,56</t>
+          <t>3,03; 11,59</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>5,39; 15,57</t>
+          <t>5,69; 15,26</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,17; 13,44</t>
+          <t>6,51; 13,78</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,1; 10,52</t>
+          <t>5,07; 10,62</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>5,37; 11,14</t>
+          <t>5,63; 11,35</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>6,26; 10,89</t>
+          <t>6,45; 11,0</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1962,63%</t>
+          <t>1980,84%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>303,95%</t>
+          <t>305,09%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>460,22%</t>
+          <t>464,73%</t>
         </is>
       </c>
     </row>
@@ -1878,32 +1878,32 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>48,06; 661,35</t>
+          <t>54,05; 645,91</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>88,99; 726,36</t>
+          <t>114,98; 781,77</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>101,65; 784,4</t>
+          <t>109,22; 776,5</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>176,61; 991,51</t>
+          <t>174,95; 1021,93</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>177,9; 993,12</t>
+          <t>197,97; 1097,32</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>207,6; 1022,05</t>
+          <t>207,04; 1088,53</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>11,76</t>
+          <t>10,38</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,47</t>
+          <t>13,37</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>9,91</t>
+          <t>11,93</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 3,94</t>
+          <t>-1,6; 3,81</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,63; 6,34</t>
+          <t>0,77; 6,49</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>8,24; 16,96</t>
+          <t>7,05; 14,09</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,23; 5,56</t>
+          <t>0,09; 5,72</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2,83; 9,09</t>
+          <t>2,37; 8,51</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,16; 14,0</t>
+          <t>9,79; 16,44</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,28; 4,15</t>
+          <t>0,09; 3,98</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>2,71; 6,61</t>
+          <t>2,59; 6,89</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>4,22; 13,25</t>
+          <t>9,76; 14,47</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>264,96%</t>
+          <t>233,9%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>162,8%</t>
+          <t>257,03%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>205,38%</t>
+          <t>247,24%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-21,85; 134,08</t>
+          <t>-28,58; 120,88</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>7,33; 206,71</t>
+          <t>11,39; 194,61</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>132,55; 541,68</t>
+          <t>114,82; 441,87</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2,17; 143,19</t>
+          <t>0,96; 142,34</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>41,8; 224,32</t>
+          <t>36,92; 209,73</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>25,42; 307,49</t>
+          <t>144,03; 405,14</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,02; 105,24</t>
+          <t>1,71; 102,16</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>49,38; 173,24</t>
+          <t>41,39; 174,47</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>87,28; 314,82</t>
+          <t>160,2; 354,01</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>5,91</t>
+          <t>10,11</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>9,94</t>
+          <t>10,17</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>7,23</t>
+          <t>10,13</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>0,64; 6,61</t>
+          <t>1,09; 6,6</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 2,46</t>
+          <t>-2,51; 2,45</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 11,95</t>
+          <t>6,94; 13,34</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 3,31</t>
+          <t>-3,77; 3,47</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-6,31; -0,14</t>
+          <t>-6,28; 0,09</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>6,38; 13,57</t>
+          <t>6,52; 13,58</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 3,95</t>
+          <t>-0,78; 3,77</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 0,15</t>
+          <t>-3,92; 0,35</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,55; 10,95</t>
+          <t>7,75; 12,59</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>143,33%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>80,24%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>72,75%</t>
+          <t>101,89%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>7,1; 123,37</t>
+          <t>13,7; 115,93</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-32,09; 44,42</t>
+          <t>-31,13; 44,01</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-18,69; 189,4</t>
+          <t>83,79; 233,04</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-26,63; 30,48</t>
+          <t>-25,74; 32,35</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-45,58; -0,95</t>
+          <t>-44,6; 0,12</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>44,1; 126,61</t>
+          <t>45,03; 125,91</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 43,08</t>
+          <t>-6,91; 41,82</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-34,33; 2,0</t>
+          <t>-35,02; 3,21</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>12,99; 116,45</t>
+          <t>66,14; 142,88</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>4,75</t>
+          <t>5,48</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>4,59</t>
+          <t>6,15</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>4,69</t>
+          <t>5,84</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>1,86; 4,32</t>
+          <t>1,77; 4,34</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>1,15; 3,59</t>
+          <t>1,15; 3,5</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2,45; 6,3</t>
+          <t>4,12; 6,99</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3,32; 6,28</t>
+          <t>3,32; 6,6</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>1,8; 4,79</t>
+          <t>1,77; 4,79</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,07; 6,22</t>
+          <t>4,76; 7,65</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,96; 4,94</t>
+          <t>2,96; 4,92</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>1,87; 3,79</t>
+          <t>1,85; 3,77</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>3,07; 5,88</t>
+          <t>4,91; 6,82</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>108,11%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>69,01%</t>
+          <t>85,94%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>32,08; 92,47</t>
+          <t>30,93; 94,82</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>20,74; 77,12</t>
+          <t>21,24; 80,27</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>47,55; 137,08</t>
+          <t>73,28; 157,65</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>36,02; 80,83</t>
+          <t>35,59; 83,3</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>19,76; 61,45</t>
+          <t>18,96; 60,66</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>24,13; 80,3</t>
+          <t>51,69; 99,98</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>40,17; 78,25</t>
+          <t>40,59; 75,44</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>26,48; 61,25</t>
+          <t>24,64; 58,31</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>44,83; 91,64</t>
+          <t>67,6; 107,19</t>
         </is>
       </c>
     </row>
